--- a/test_files/tags.xlsx
+++ b/test_files/tags.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20655" windowHeight="17055"/>
+    <workbookView windowWidth="18350" windowHeight="7000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="113">
   <si>
     <t>注：1、将excel文件名命名为试卷ID；2、选择题的选项直接录ABCD；3、试卷有多少题就写多少题号，不要有多余行。</t>
   </si>
@@ -36,7 +36,7 @@
     <t>学校：</t>
   </si>
   <si>
-    <t>BS-LJBS</t>
+    <t>NK-NY</t>
   </si>
   <si>
     <t>试题时间：</t>
@@ -48,9 +48,6 @@
     <t>试卷说明：</t>
   </si>
   <si>
-    <t>2024-8-2初试</t>
-  </si>
-  <si>
     <t>（说明可以为空）</t>
   </si>
   <si>
@@ -84,7 +81,7 @@
     <t>填空题1</t>
   </si>
   <si>
-    <t>343</t>
+    <t>19</t>
   </si>
   <si>
     <t>应用题模块</t>
@@ -93,175 +90,166 @@
     <t>填空题2</t>
   </si>
   <si>
-    <t>18</t>
+    <t>200</t>
   </si>
   <si>
     <t>填空题3</t>
   </si>
   <si>
-    <t>98</t>
+    <t>13</t>
   </si>
   <si>
     <t>填空题4</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>填空题5</t>
   </si>
   <si>
-    <t>25</t>
+    <t>150</t>
+  </si>
+  <si>
+    <t>行程模块</t>
   </si>
   <si>
     <t>填空题6</t>
   </si>
   <si>
-    <t>42</t>
+    <t>1又3/5</t>
+  </si>
+  <si>
+    <t>计算模块</t>
   </si>
   <si>
     <t>填空题7</t>
   </si>
   <si>
-    <t>202.5</t>
-  </si>
-  <si>
-    <t>计算模块</t>
+    <t>2.4</t>
   </si>
   <si>
     <t>填空题8</t>
   </si>
   <si>
-    <t>8</t>
+    <t>216000</t>
+  </si>
+  <si>
+    <t>填空题9</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>几何模块</t>
   </si>
   <si>
-    <t>填空题9</t>
-  </si>
-  <si>
-    <t>6.772</t>
-  </si>
-  <si>
     <t>填空题10</t>
   </si>
   <si>
-    <t>4</t>
+    <t>15</t>
   </si>
   <si>
     <t>填空题11</t>
   </si>
   <si>
-    <t>13</t>
+    <t>16又4/11</t>
   </si>
   <si>
     <t>填空题12</t>
   </si>
   <si>
-    <t>16又9/11</t>
+    <t>3</t>
   </si>
   <si>
     <t>填空题13</t>
   </si>
   <si>
-    <t>10000</t>
+    <t>15.75</t>
   </si>
   <si>
     <t>填空题14</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>填空题15</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>填空题16</t>
+    <t>20</t>
   </si>
   <si>
     <t>计算题1</t>
   </si>
   <si>
-    <t>21/22</t>
+    <t>x=1</t>
   </si>
   <si>
     <t>计算题2</t>
   </si>
   <si>
-    <t>x=29</t>
+    <t>501/202</t>
   </si>
   <si>
     <t>计算题3</t>
   </si>
   <si>
-    <t>x=2，y=1</t>
+    <t>x=5/3</t>
   </si>
   <si>
     <t>计算题4</t>
   </si>
   <si>
-    <t>x=3</t>
-  </si>
-  <si>
-    <t>解答题1（1）</t>
-  </si>
-  <si>
-    <t>②③</t>
-  </si>
-  <si>
-    <t>解答题1（2）</t>
-  </si>
-  <si>
-    <t>与解析一致</t>
-  </si>
-  <si>
-    <t>解答题2（1）</t>
-  </si>
-  <si>
-    <t>95.5</t>
-  </si>
-  <si>
-    <t>解答题2（2）</t>
-  </si>
-  <si>
-    <t>16又2/3</t>
-  </si>
-  <si>
-    <t>解答题2（3）</t>
-  </si>
-  <si>
-    <t>解答题3（1）</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>解答题3（2）</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>解答题4（1）</t>
-  </si>
-  <si>
-    <t>5/6或1/2</t>
-  </si>
-  <si>
-    <t>解答题4（2）</t>
-  </si>
-  <si>
-    <t>30s或70s</t>
-  </si>
-  <si>
-    <t>解答题4（3）</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>123</t>
+  </si>
+  <si>
+    <t>计算题5</t>
+  </si>
+  <si>
+    <t>157/126</t>
+  </si>
+  <si>
+    <t>计算题6</t>
+  </si>
+  <si>
+    <t>36288</t>
+  </si>
+  <si>
+    <t>计算题7</t>
+  </si>
+  <si>
+    <t>1/1012</t>
+  </si>
+  <si>
+    <t>解决问题1</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>解决问题2</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>解决问题3</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>解决问题4</t>
+  </si>
+  <si>
+    <t>解决问题5</t>
+  </si>
+  <si>
+    <t>8,6,12</t>
+  </si>
+  <si>
+    <t>解决问题6</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>解决问题7</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>分数线：</t>
@@ -1190,6 +1178,8 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1199,8 +1189,6 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1520,10 +1508,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:N33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11.7333333333333" style="25" customWidth="1"/>
+    <col min="1" max="1" width="10.4166666666667" style="25" customWidth="1"/>
     <col min="2" max="2" width="21.6666666666667" style="25" customWidth="1"/>
     <col min="3" max="3" width="15" style="25" customWidth="1"/>
     <col min="4" max="4" width="18.8333333333333" style="25" customWidth="1"/>
@@ -1555,7 +1543,7 @@
       <c r="M1" s="27"/>
       <c r="N1" s="27"/>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:2">
       <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
@@ -1563,7 +1551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:2">
       <c r="A3" s="29" t="s">
         <v>3</v>
       </c>
@@ -1571,70 +1559,68 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:3">
       <c r="A4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="25" t="s">
         <v>6</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="C5" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="D5" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="E5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="F5" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="G5" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="H5" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="I5" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="35"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="37"/>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>18</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
-      <c r="F6" s="36">
-        <v>0</v>
-      </c>
-      <c r="G6" s="37">
-        <v>3</v>
+      <c r="F6" s="33">
+        <v>0</v>
+      </c>
+      <c r="G6" s="34">
+        <v>2</v>
       </c>
       <c r="H6" s="15"/>
       <c r="I6" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
@@ -1644,23 +1630,23 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>20</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>21</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
-      <c r="F7" s="36">
-        <v>0</v>
-      </c>
-      <c r="G7" s="37">
-        <v>3</v>
+      <c r="F7" s="33">
+        <v>0</v>
+      </c>
+      <c r="G7" s="34">
+        <v>2</v>
       </c>
       <c r="H7" s="15"/>
       <c r="I7" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
@@ -1670,23 +1656,23 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>22</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>23</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="36">
-        <v>0</v>
-      </c>
-      <c r="G8" s="37">
-        <v>3</v>
+      <c r="F8" s="33">
+        <v>0</v>
+      </c>
+      <c r="G8" s="34">
+        <v>2</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
@@ -1696,23 +1682,23 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
-      <c r="F9" s="36">
-        <v>0</v>
-      </c>
-      <c r="G9" s="37">
-        <v>3</v>
+      <c r="F9" s="33">
+        <v>0</v>
+      </c>
+      <c r="G9" s="34">
+        <v>2</v>
       </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
@@ -1722,23 +1708,23 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
-      <c r="F10" s="36">
-        <v>0</v>
-      </c>
-      <c r="G10" s="37">
-        <v>3</v>
+      <c r="F10" s="33">
+        <v>0</v>
+      </c>
+      <c r="G10" s="34">
+        <v>2</v>
       </c>
       <c r="H10" s="15"/>
       <c r="I10" s="15" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
@@ -1748,23 +1734,23 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>29</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
-      <c r="F11" s="36">
-        <v>0</v>
-      </c>
-      <c r="G11" s="37">
-        <v>3</v>
+      <c r="F11" s="33">
+        <v>0</v>
+      </c>
+      <c r="G11" s="34">
+        <v>2</v>
       </c>
       <c r="H11" s="15"/>
       <c r="I11" s="15" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
@@ -1782,15 +1768,15 @@
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
-      <c r="F12" s="36">
-        <v>0</v>
-      </c>
-      <c r="G12" s="37">
-        <v>3</v>
+      <c r="F12" s="33">
+        <v>0</v>
+      </c>
+      <c r="G12" s="34">
+        <v>2</v>
       </c>
       <c r="H12" s="15"/>
       <c r="I12" s="15" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
@@ -1800,23 +1786,23 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>33</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>34</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
-      <c r="F13" s="36">
-        <v>0</v>
-      </c>
-      <c r="G13" s="37">
-        <v>3</v>
+      <c r="F13" s="33">
+        <v>0</v>
+      </c>
+      <c r="G13" s="34">
+        <v>2</v>
       </c>
       <c r="H13" s="15"/>
       <c r="I13" s="15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
@@ -1826,23 +1812,23 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
-      <c r="F14" s="36">
-        <v>0</v>
-      </c>
-      <c r="G14" s="37">
-        <v>3</v>
+      <c r="F14" s="33">
+        <v>0</v>
+      </c>
+      <c r="G14" s="34">
+        <v>2</v>
       </c>
       <c r="H14" s="15"/>
       <c r="I14" s="15" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
@@ -1852,23 +1838,23 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>38</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>39</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
-      <c r="F15" s="36">
-        <v>0</v>
-      </c>
-      <c r="G15" s="37">
-        <v>3</v>
+      <c r="F15" s="33">
+        <v>0</v>
+      </c>
+      <c r="G15" s="34">
+        <v>2</v>
       </c>
       <c r="H15" s="15"/>
       <c r="I15" s="15" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
@@ -1878,23 +1864,23 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>40</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>41</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
-      <c r="F16" s="36">
-        <v>0</v>
-      </c>
-      <c r="G16" s="37">
-        <v>3</v>
+      <c r="F16" s="33">
+        <v>0</v>
+      </c>
+      <c r="G16" s="34">
+        <v>2</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
@@ -1904,23 +1890,23 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="15" t="s">
         <v>42</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>43</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
-      <c r="F17" s="36">
-        <v>0</v>
-      </c>
-      <c r="G17" s="37">
-        <v>3</v>
+      <c r="F17" s="33">
+        <v>0</v>
+      </c>
+      <c r="G17" s="34">
+        <v>2</v>
       </c>
       <c r="H17" s="15"/>
       <c r="I17" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
@@ -1930,23 +1916,23 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>45</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
-      <c r="F18" s="36">
-        <v>0</v>
-      </c>
-      <c r="G18" s="37">
-        <v>3</v>
+      <c r="F18" s="33">
+        <v>0</v>
+      </c>
+      <c r="G18" s="34">
+        <v>2</v>
       </c>
       <c r="H18" s="15"/>
       <c r="I18" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
@@ -1956,23 +1942,23 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>46</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>47</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
-      <c r="F19" s="36">
-        <v>0</v>
-      </c>
-      <c r="G19" s="37">
-        <v>3</v>
+      <c r="F19" s="33">
+        <v>0</v>
+      </c>
+      <c r="G19" s="34">
+        <v>2</v>
       </c>
       <c r="H19" s="15"/>
       <c r="I19" s="15" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
@@ -1982,23 +1968,23 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>48</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>49</v>
       </c>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
-      <c r="F20" s="36">
-        <v>0</v>
-      </c>
-      <c r="G20" s="37">
-        <v>3</v>
+      <c r="F20" s="33">
+        <v>0</v>
+      </c>
+      <c r="G20" s="34">
+        <v>4</v>
       </c>
       <c r="H20" s="15"/>
       <c r="I20" s="15" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
@@ -2008,23 +1994,23 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="15" t="s">
         <v>50</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>34</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
-      <c r="F21" s="36">
-        <v>0</v>
-      </c>
-      <c r="G21" s="37">
-        <v>3</v>
+      <c r="F21" s="33">
+        <v>0</v>
+      </c>
+      <c r="G21" s="34">
+        <v>4</v>
       </c>
       <c r="H21" s="15"/>
       <c r="I21" s="15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
@@ -2042,15 +2028,15 @@
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
-      <c r="F22" s="36">
-        <v>0</v>
-      </c>
-      <c r="G22" s="37">
-        <v>3</v>
+      <c r="F22" s="33">
+        <v>0</v>
+      </c>
+      <c r="G22" s="34">
+        <v>4</v>
       </c>
       <c r="H22" s="15"/>
       <c r="I22" s="15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
@@ -2068,15 +2054,15 @@
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
-      <c r="F23" s="36">
-        <v>0</v>
-      </c>
-      <c r="G23" s="37">
-        <v>3</v>
+      <c r="F23" s="33">
+        <v>0</v>
+      </c>
+      <c r="G23" s="34">
+        <v>4</v>
       </c>
       <c r="H23" s="15"/>
       <c r="I23" s="15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J23" s="15"/>
       <c r="K23" s="15"/>
@@ -2094,15 +2080,15 @@
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
-      <c r="F24" s="36">
-        <v>0</v>
-      </c>
-      <c r="G24" s="37">
-        <v>3</v>
+      <c r="F24" s="33">
+        <v>0</v>
+      </c>
+      <c r="G24" s="34">
+        <v>4</v>
       </c>
       <c r="H24" s="15"/>
       <c r="I24" s="15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
@@ -2120,15 +2106,15 @@
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
-      <c r="F25" s="36">
-        <v>0</v>
-      </c>
-      <c r="G25" s="37">
-        <v>3</v>
+      <c r="F25" s="33">
+        <v>0</v>
+      </c>
+      <c r="G25" s="34">
+        <v>4</v>
       </c>
       <c r="H25" s="15"/>
       <c r="I25" s="15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
@@ -2146,15 +2132,15 @@
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
       <c r="E26" s="15"/>
-      <c r="F26" s="36">
-        <v>0</v>
-      </c>
-      <c r="G26" s="37">
-        <v>5</v>
+      <c r="F26" s="33">
+        <v>0</v>
+      </c>
+      <c r="G26" s="34">
+        <v>4</v>
       </c>
       <c r="H26" s="15"/>
       <c r="I26" s="15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J26" s="15"/>
       <c r="K26" s="15"/>
@@ -2172,15 +2158,15 @@
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
-      <c r="F27" s="36">
-        <v>0</v>
-      </c>
-      <c r="G27" s="37">
-        <v>5</v>
+      <c r="F27" s="33">
+        <v>0</v>
+      </c>
+      <c r="G27" s="34">
+        <v>6</v>
       </c>
       <c r="H27" s="15"/>
       <c r="I27" s="15" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J27" s="15"/>
       <c r="K27" s="15"/>
@@ -2198,15 +2184,15 @@
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
-      <c r="F28" s="36">
-        <v>0</v>
-      </c>
-      <c r="G28" s="37">
-        <v>3</v>
+      <c r="F28" s="33">
+        <v>0</v>
+      </c>
+      <c r="G28" s="34">
+        <v>6</v>
       </c>
       <c r="H28" s="15"/>
       <c r="I28" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
@@ -2224,15 +2210,15 @@
       <c r="C29" s="15"/>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
-      <c r="F29" s="36">
-        <v>0</v>
-      </c>
-      <c r="G29" s="37">
-        <v>3</v>
+      <c r="F29" s="33">
+        <v>0</v>
+      </c>
+      <c r="G29" s="34">
+        <v>6</v>
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J29" s="15"/>
       <c r="K29" s="15"/>
@@ -2250,15 +2236,15 @@
       <c r="C30" s="15"/>
       <c r="D30" s="15"/>
       <c r="E30" s="15"/>
-      <c r="F30" s="36">
-        <v>0</v>
-      </c>
-      <c r="G30" s="37">
-        <v>4</v>
+      <c r="F30" s="33">
+        <v>0</v>
+      </c>
+      <c r="G30" s="34">
+        <v>6</v>
       </c>
       <c r="H30" s="15"/>
       <c r="I30" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J30" s="15"/>
       <c r="K30" s="15"/>
@@ -2276,15 +2262,15 @@
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
       <c r="E31" s="15"/>
-      <c r="F31" s="36">
-        <v>0</v>
-      </c>
-      <c r="G31" s="37">
-        <v>5</v>
+      <c r="F31" s="33">
+        <v>0</v>
+      </c>
+      <c r="G31" s="34">
+        <v>6</v>
       </c>
       <c r="H31" s="15"/>
       <c r="I31" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J31" s="15"/>
       <c r="K31" s="15"/>
@@ -2302,15 +2288,15 @@
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="15"/>
-      <c r="F32" s="36">
-        <v>0</v>
-      </c>
-      <c r="G32" s="37">
-        <v>5</v>
+      <c r="F32" s="33">
+        <v>0</v>
+      </c>
+      <c r="G32" s="34">
+        <v>7</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J32" s="15"/>
       <c r="K32" s="15"/>
@@ -2328,73 +2314,21 @@
       <c r="C33" s="15"/>
       <c r="D33" s="15"/>
       <c r="E33" s="15"/>
-      <c r="F33" s="36">
-        <v>0</v>
-      </c>
-      <c r="G33" s="37">
-        <v>3</v>
+      <c r="F33" s="33">
+        <v>0</v>
+      </c>
+      <c r="G33" s="34">
+        <v>7</v>
       </c>
       <c r="H33" s="15"/>
       <c r="I33" s="15" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="J33" s="15"/>
       <c r="K33" s="15"/>
       <c r="L33" s="15"/>
       <c r="M33" s="15"/>
       <c r="N33" s="15"/>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="36">
-        <v>0</v>
-      </c>
-      <c r="G34" s="37">
-        <v>3</v>
-      </c>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="36">
-        <v>0</v>
-      </c>
-      <c r="G35" s="37">
-        <v>4</v>
-      </c>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2410,7 +2344,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.3333333333333" customWidth="1"/>
     <col min="2" max="2" width="8.5" customWidth="1"/>
@@ -2420,10 +2354,10 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
@@ -2441,13 +2375,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
@@ -2456,10 +2390,10 @@
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="D4" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F4" s="11"/>
     </row>
@@ -2470,10 +2404,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2483,7 +2417,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F6" s="14"/>
     </row>
@@ -2494,7 +2428,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F7" s="14"/>
     </row>
@@ -2505,7 +2439,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F8" s="14"/>
     </row>
@@ -2516,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F9" s="14"/>
     </row>
@@ -2527,7 +2461,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F10" s="16"/>
     </row>
@@ -2538,10 +2472,10 @@
         <v>7</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2551,7 +2485,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F12" s="19"/>
     </row>
@@ -2562,7 +2496,7 @@
         <v>9</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F13" s="19"/>
     </row>
@@ -2573,7 +2507,7 @@
         <v>10</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F14" s="19"/>
     </row>
@@ -2584,7 +2518,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F15" s="19"/>
     </row>
@@ -2595,7 +2529,7 @@
         <v>12</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F16" s="19"/>
     </row>
@@ -2606,7 +2540,7 @@
         <v>13</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F17" s="19"/>
     </row>
@@ -2617,7 +2551,7 @@
         <v>14</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F18" s="19"/>
     </row>
@@ -2628,7 +2562,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F19" s="19"/>
     </row>
@@ -2639,7 +2573,7 @@
         <v>16</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F20" s="19"/>
     </row>
@@ -2650,7 +2584,7 @@
         <v>17</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F21" s="19"/>
     </row>
@@ -2661,7 +2595,7 @@
         <v>18</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F22" s="20"/>
     </row>
@@ -2672,10 +2606,10 @@
         <v>19</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2685,7 +2619,7 @@
         <v>20</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F24" s="23"/>
     </row>
@@ -2696,7 +2630,7 @@
         <v>21</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F25" s="23"/>
     </row>
@@ -2707,7 +2641,7 @@
         <v>22</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F26" s="23"/>
     </row>
@@ -2718,7 +2652,7 @@
         <v>23</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F27" s="23"/>
     </row>
@@ -2729,7 +2663,7 @@
         <v>24</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F28" s="23"/>
     </row>
@@ -2740,7 +2674,7 @@
         <v>25</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F29" s="23"/>
     </row>
@@ -2751,7 +2685,7 @@
         <v>26</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F30" s="23"/>
     </row>
@@ -2762,7 +2696,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F31" s="23"/>
     </row>
@@ -2773,7 +2707,7 @@
         <v>28</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F32" s="23"/>
     </row>
@@ -2784,16 +2718,16 @@
         <v>29</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F33" s="23"/>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="4:6">
       <c r="D34" s="21">
         <v>30</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F34" s="24"/>
     </row>
